--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00:00</t>
+          <t>2026-10-22 09:15:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:30:00</t>
+          <t>2026-10-22 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-22 11:30:00</t>
+          <t>2026-10-22 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45:00</t>
+          <t>2026-10-22 10:40:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 11:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 11:45:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2870,156 +2870,1297 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-10-22 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Buxoro</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-10-22 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb II</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cibalia</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dubrava Zagreb</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kustošija</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sesvete</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hrvace</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sidama Bunna</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Awassa Kenema</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Bahardar</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>-1</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G23">

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6">

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6">

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU23"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G20">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N20">
@@ -3672,495 +3672,6 @@
         <v>0</v>
       </c>
       <c r="AU20" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sesvete</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Hrvace</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Bahardar</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Welwalo Adigrat Uni</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>-1</v>
-      </c>
-      <c r="AN22">
-        <v>-1</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>-1</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sidama Bunna</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Awassa Kenema</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-22 10:40:00</t>
+          <t>2026-10-22 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:30:00</t>
+          <t>2026-10-22 10:40:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45:00</t>
+          <t>2026-10-22 11:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00:00</t>
+          <t>2026-10-22 11:45:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Al Gharafa</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Al Ahli</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00:00</t>
+          <t>2026-10-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-22 19:00:00</t>
+          <t>2026-10-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-22 19:00:00</t>
+          <t>2026-10-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G19">
@@ -3509,169 +3509,6 @@
         <v>0</v>
       </c>
       <c r="AU19" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sidama Bunna</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Awassa Kenema</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q7">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>4.14</v>
@@ -813,16 +813,16 @@
         <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.06</v>
@@ -852,10 +852,10 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
         <v>1.24</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="O7">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>7.65</v>
       </c>
       <c r="O13">
         <v>5</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q13">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
         <v>3.3</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
         <v>5.36</v>
@@ -1465,10 +1465,10 @@
         <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U7">
         <v>2.58</v>
@@ -1477,7 +1477,7 @@
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -2111,22 +2111,22 @@
         <v>10.7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2135,31 +2135,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>5</v>
       </c>
       <c r="P13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>1.79</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>4.14</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.19</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
-        <v>5.36</v>
+        <v>4.26</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB7">
         <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD7">
         <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2437,25 +2437,25 @@
         <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>6.46</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="T13">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="W13">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2485,7 +2485,7 @@
         <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.07</v>
+        <v>3.2</v>
       </c>
       <c r="AK13">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -692,7 +692,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -807,71 +807,71 @@
         <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
         <v>1.38</v>
       </c>
       <c r="AE3">
+        <v>1.13</v>
+      </c>
+      <c r="AF3">
+        <v>1.67</v>
+      </c>
+      <c r="AG3">
+        <v>2.05</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.11</v>
       </c>
-      <c r="AF3">
-        <v>1.72</v>
-      </c>
-      <c r="AG3">
-        <v>2.02</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.24</v>
-      </c>
       <c r="AK3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
         <v>1.74</v>
@@ -2470,7 +2470,7 @@
         <v>1.22</v>
       </c>
       <c r="AB13">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AC13">
         <v>1.64</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q17">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2443,16 +2443,16 @@
         <v>3</v>
       </c>
       <c r="S13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T13">
         <v>5</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W13">
         <v>1.29</v>
@@ -2467,25 +2467,25 @@
         <v>8.1</v>
       </c>
       <c r="AA13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB13">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AC13">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AD13">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AE13">
         <v>1.45</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
         <v>1.06</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2485,7 +2485,7 @@
         <v>1.43</v>
       </c>
       <c r="AG13">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -644,7 +644,7 @@
         <v>1.93</v>
       </c>
       <c r="Q2">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="R2">
         <v>2.05</v>
@@ -668,7 +668,7 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
         <v>3.38</v>
@@ -683,16 +683,16 @@
         <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
         <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -825,7 +825,7 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.04</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
         <v>2.84</v>
@@ -1474,10 +1474,10 @@
         <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1486,7 +1486,7 @@
         <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="AA7">
         <v>1.84</v>
@@ -2271,58 +2271,58 @@
         <v>3.28</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.11</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q13">
         <v>6</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -641,7 +641,7 @@
         <v>3.3</v>
       </c>
       <c r="P2">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>3.8</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O3">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -840,7 +840,7 @@
         <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -1492,7 +1492,7 @@
         <v>1.84</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC7">
         <v>3.08</v>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O12">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q12">
         <v>2.79</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P14">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q14">
         <v>3.45</v>
@@ -2612,7 +2612,7 @@
         <v>3.72</v>
       </c>
       <c r="U14">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
         <v>1.6</v>
@@ -2630,7 +2630,7 @@
         <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
         <v>2.36</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>5.94</v>
       </c>
       <c r="P17">
-        <v>9.050000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="Q17">
         <v>1.68</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU19"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>1.34</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O16">
         <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45:00</t>
+          <t>2026-10-22 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,14 +3048,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Al Gharafa</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Al Ahli</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>5.94</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>7.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q17">
-        <v>1.68</v>
+        <v>2.61</v>
       </c>
       <c r="R17">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="S17">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="U17">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="V17">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>5.22</v>
+        <v>5.51</v>
       </c>
       <c r="AA17">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB17">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AC17">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="AD17">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE17">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF17">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00:00</t>
+          <t>2026-10-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,68 +3239,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3374,141 +3374,304 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Bahardar</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Welwalo Adigrat Uni</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Sidama Bunna</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Awassa Kenema</t>
         </is>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -2274,10 +2274,10 @@
         <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S12">
         <v>1.37</v>
@@ -2304,7 +2304,7 @@
         <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
         <v>1.79</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P13">
         <v>1.34</v>
@@ -2452,7 +2452,7 @@
         <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W13">
         <v>1.29</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z13">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA13">
         <v>1.25</v>
       </c>
       <c r="AB13">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AC13">
         <v>1.67</v>
@@ -2482,10 +2482,10 @@
         <v>1.45</v>
       </c>
       <c r="AF13">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="AK13">
         <v>1.06</v>
@@ -2630,7 +2630,7 @@
         <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
         <v>2.36</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q17">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="R17">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
         <v>1.14</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>5.51</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC17">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="O18">
         <v>5.94</v>
       </c>
       <c r="P18">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R18">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
         <v>1.16</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>3.3</v>
@@ -668,25 +668,25 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AA2">
         <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
         <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>1.72</v>
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
+        <v>2.38</v>
+      </c>
+      <c r="R3">
         <v>2.25</v>
       </c>
-      <c r="R3">
-        <v>2.3</v>
-      </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA3">
         <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
         <v>3.55</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
         <v>4.26</v>
@@ -1465,10 +1465,10 @@
         <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U7">
         <v>2.62</v>
@@ -1486,7 +1486,7 @@
         <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
         <v>1.84</v>
@@ -1495,7 +1495,7 @@
         <v>1.88</v>
       </c>
       <c r="AC7">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD7">
         <v>1.28</v>
@@ -1504,7 +1504,7 @@
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
         <v>1.91</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
         <v>1.08</v>
@@ -2111,22 +2111,22 @@
         <v>10.7</v>
       </c>
       <c r="Q11">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="U11">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2135,28 +2135,28 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AG11">
         <v>1.51</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK11">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.9</v>
+        <v>6.23</v>
       </c>
       <c r="O13">
-        <v>4.9</v>
+        <v>5.55</v>
       </c>
       <c r="P13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -2470,7 +2470,7 @@
         <v>1.25</v>
       </c>
       <c r="AB13">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AC13">
         <v>1.67</v>
@@ -2485,7 +2485,7 @@
         <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O14">
         <v>3.75</v>
       </c>
       <c r="P14">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q14">
         <v>3.45</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -3086,19 +3086,19 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
         <v>2.45</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S17">
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
         <v>2.13</v>
@@ -3107,7 +3107,7 @@
         <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3125,10 +3125,10 @@
         <v>2.7</v>
       </c>
       <c r="AC17">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE17">
         <v>1.25</v>
@@ -3246,7 +3246,7 @@
         <v>1.33</v>
       </c>
       <c r="O18">
-        <v>5.94</v>
+        <v>5.5</v>
       </c>
       <c r="P18">
         <v>8</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.36</v>
       </c>
       <c r="T2">
+        <v>3.2</v>
+      </c>
+      <c r="U2">
+        <v>2.47</v>
+      </c>
+      <c r="V2">
+        <v>1.46</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>3.82</v>
+      </c>
+      <c r="AA2">
+        <v>1.76</v>
+      </c>
+      <c r="AB2">
+        <v>1.92</v>
+      </c>
+      <c r="AC2">
         <v>2.88</v>
       </c>
-      <c r="U2">
-        <v>2.88</v>
-      </c>
-      <c r="V2">
-        <v>1.36</v>
-      </c>
-      <c r="W2">
-        <v>1.08</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.3</v>
-      </c>
-      <c r="Z2">
-        <v>3.41</v>
-      </c>
-      <c r="AA2">
-        <v>1.9</v>
-      </c>
-      <c r="AB2">
-        <v>1.85</v>
-      </c>
-      <c r="AC2">
-        <v>3.2</v>
-      </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
         <v>1.36</v>
       </c>
       <c r="T3">
+        <v>2.88</v>
+      </c>
+      <c r="U3">
+        <v>2.88</v>
+      </c>
+      <c r="V3">
+        <v>1.36</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
+        <v>3.41</v>
+      </c>
+      <c r="AA3">
+        <v>1.9</v>
+      </c>
+      <c r="AB3">
+        <v>1.85</v>
+      </c>
+      <c r="AC3">
         <v>3.2</v>
       </c>
-      <c r="U3">
-        <v>2.47</v>
-      </c>
-      <c r="V3">
-        <v>1.46</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.82</v>
-      </c>
-      <c r="AA3">
-        <v>1.76</v>
-      </c>
-      <c r="AB3">
-        <v>1.92</v>
-      </c>
-      <c r="AC3">
-        <v>2.88</v>
-      </c>
       <c r="AD3">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="O11">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="P11">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="Q11">
         <v>1.69</v>
@@ -2129,16 +2129,16 @@
         <v>1.43</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
         <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
         <v>1.79</v>
@@ -2153,7 +2153,7 @@
         <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
         <v>2.32</v>
@@ -2926,34 +2926,34 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
         <v>2.07</v>
@@ -2962,19 +2962,19 @@
         <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O2">
         <v>3.4</v>
@@ -650,22 +650,22 @@
         <v>2.25</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
         <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.25</v>
@@ -680,10 +680,10 @@
         <v>1.92</v>
       </c>
       <c r="AC2">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.14</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.87</v>
@@ -810,25 +810,25 @@
         <v>3.8</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
@@ -837,13 +837,13 @@
         <v>3.41</v>
       </c>
       <c r="AA3">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
         <v>1.26</v>
@@ -855,7 +855,7 @@
         <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
         <v>1.16</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="P5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>3.85</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="R7">
         <v>2.05</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
         <v>1.4</v>
@@ -1480,13 +1480,13 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
         <v>1.84</v>
@@ -1498,13 +1498,13 @@
         <v>3.25</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG7">
         <v>1.91</v>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-22 10:30:00</t>
+          <t>2026-10-22 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.13</v>
+        <v>1.2</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="P12">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="Q12">
-        <v>2.64</v>
+        <v>1.69</v>
       </c>
       <c r="R12">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T12">
-        <v>2.68</v>
+        <v>3.19</v>
       </c>
       <c r="U12">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
         <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:40:00</t>
+          <t>2026-10-22 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.23</v>
+        <v>2.13</v>
       </c>
       <c r="O13">
-        <v>5.55</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="S13">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="U13">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
+        <v>1.27</v>
+      </c>
+      <c r="Z13">
+        <v>3.14</v>
+      </c>
+      <c r="AA13">
+        <v>1.95</v>
+      </c>
+      <c r="AB13">
+        <v>1.79</v>
+      </c>
+      <c r="AC13">
+        <v>3.2</v>
+      </c>
+      <c r="AD13">
+        <v>1.26</v>
+      </c>
+      <c r="AE13">
         <v>1.06</v>
       </c>
-      <c r="Z13">
-        <v>8.5</v>
-      </c>
-      <c r="AA13">
-        <v>1.25</v>
-      </c>
-      <c r="AB13">
-        <v>3.75</v>
-      </c>
-      <c r="AC13">
-        <v>1.67</v>
-      </c>
-      <c r="AD13">
-        <v>2.17</v>
-      </c>
-      <c r="AE13">
-        <v>1.45</v>
-      </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-22 11:30:00</t>
+          <t>2026-10-22 10:40:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.98</v>
+        <v>5.9</v>
       </c>
       <c r="O14">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="P14">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="Q14">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T14">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z14">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AB14">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AF14">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
         <v>2.5</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="AK14">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45:00</t>
+          <t>2026-10-22 11:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="O15">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>9</v>
+        <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA15">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00:00</t>
+          <t>2026-10-22 11:45:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="R16">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>2.72</v>
+        <v>2.13</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AC16">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
+        <v>1.73</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.07</v>
       </c>
-      <c r="AF16">
-        <v>1.96</v>
-      </c>
-      <c r="AG16">
-        <v>1.73</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.16</v>
-      </c>
       <c r="AK16">
-        <v>2.27</v>
+        <v>3.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-22 13:00:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="U17">
-        <v>2.13</v>
+        <v>2.76</v>
       </c>
       <c r="V17">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB17">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC17">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD17">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45:00</t>
+          <t>2026-10-22 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Al Gharafa</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Al Ahli</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S18">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="V18">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>5.22</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC18">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AD18">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE18">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00:00</t>
+          <t>2026-10-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-22 21:00:00</t>
+          <t>2026-10-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3537,141 +3537,304 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Bahardar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Welwalo Adigrat Uni</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Sidama Bunna</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Awassa Kenema</t>
         </is>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4">
@@ -961,52 +961,52 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O4">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="P4">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q4">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="U4">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Z4">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AA4">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AD4">
         <v>1.08</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="O5">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="P5">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="R5">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S5">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T5">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
         <v>1.01</v>
       </c>
       <c r="X5">
+        <v>1.06</v>
+      </c>
+      <c r="Y5">
+        <v>1.53</v>
+      </c>
+      <c r="Z5">
+        <v>2.28</v>
+      </c>
+      <c r="AA5">
+        <v>2.75</v>
+      </c>
+      <c r="AB5">
+        <v>1.37</v>
+      </c>
+      <c r="AC5">
+        <v>5.55</v>
+      </c>
+      <c r="AD5">
         <v>1.08</v>
       </c>
-      <c r="Y5">
-        <v>1.61</v>
-      </c>
-      <c r="Z5">
-        <v>2.13</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>1.36</v>
-      </c>
-      <c r="AC5">
-        <v>6.3</v>
-      </c>
-      <c r="AD5">
-        <v>1.06</v>
-      </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AG5">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
         <v>2.72</v>
       </c>
       <c r="P6">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S6">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="T6">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="U6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V6">
         <v>1.2</v>
@@ -1317,13 +1317,13 @@
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z6">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -1332,19 +1332,19 @@
         <v>1.36</v>
       </c>
       <c r="AC6">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AG6">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R10">
         <v>2.23</v>
@@ -1957,34 +1957,34 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD10">
         <v>1.28</v>
@@ -1993,10 +1993,10 @@
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="O12">
         <v>5.25</v>
       </c>
       <c r="P12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="U12">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
         <v>3.5</v>
@@ -2310,19 +2310,19 @@
         <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="AG12">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1.37</v>
       </c>
       <c r="T13">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
         <v>2.72</v>
@@ -2455,7 +2455,7 @@
         <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2467,7 +2467,7 @@
         <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB13">
         <v>1.79</v>
@@ -2476,7 +2476,7 @@
         <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
         <v>1.06</v>
@@ -2485,7 +2485,7 @@
         <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>4.9</v>
       </c>
       <c r="P14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -2606,10 +2606,10 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="U14">
         <v>1.81</v>
@@ -2648,7 +2648,7 @@
         <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>3.1</v>
       </c>
       <c r="AK14">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R15">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2778,7 +2778,7 @@
         <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W15">
         <v>1.13</v>
@@ -2793,7 +2793,7 @@
         <v>4.8</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB15">
         <v>2.36</v>
@@ -2811,7 +2811,7 @@
         <v>1.46</v>
       </c>
       <c r="AG15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>1.53</v>
       </c>
       <c r="AB16">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AC16">
         <v>2.1</v>
@@ -3255,37 +3255,37 @@
         <v>2.45</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U18">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB18">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AC18">
         <v>2.05</v>
@@ -3294,13 +3294,13 @@
         <v>1.66</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG18">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1.33</v>
       </c>
       <c r="O19">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="P19">
         <v>7.5</v>
@@ -3427,7 +3427,7 @@
         <v>4.05</v>
       </c>
       <c r="U19">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="V19">
         <v>1.63</v>
@@ -3436,34 +3436,34 @@
         <v>1.16</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="AA19">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB19">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC19">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD19">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -644,7 +644,7 @@
         <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="R2">
         <v>2.25</v>
@@ -671,7 +671,7 @@
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="AA2">
         <v>1.76</v>
@@ -680,7 +680,7 @@
         <v>1.92</v>
       </c>
       <c r="AC2">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD2">
         <v>1.33</v>
@@ -816,7 +816,7 @@
         <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="U3">
         <v>2.75</v>
@@ -834,7 +834,7 @@
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="AA3">
         <v>1.95</v>
@@ -852,7 +852,7 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
         <v>2</v>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>2.13</v>
       </c>
       <c r="AA6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB6">
         <v>1.36</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V7">
         <v>1.4</v>
@@ -1492,7 +1492,7 @@
         <v>1.84</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
         <v>3.25</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>6.1</v>
       </c>
       <c r="Q10">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1996,7 +1996,7 @@
         <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="O12">
         <v>5.25</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q12">
         <v>1.67</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>2.64</v>
@@ -2467,10 +2467,10 @@
         <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="O14">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="P14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -2609,13 +2609,13 @@
         <v>1.1</v>
       </c>
       <c r="T14">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="U14">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="W14">
         <v>1.29</v>
@@ -2627,28 +2627,28 @@
         <v>1.06</v>
       </c>
       <c r="Z14">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB14">
         <v>4.1</v>
       </c>
       <c r="AC14">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF14">
         <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
         <v>2.05</v>
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V18">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD18">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE18">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
         <v>1.39</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>5.5</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>7.35</v>
       </c>
       <c r="Q19">
         <v>1.67</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -970,71 +970,71 @@
         <v>2.85</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="S4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="T4">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Z4">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AA4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB4">
+        <v>1.31</v>
+      </c>
+      <c r="AC4">
+        <v>5.8</v>
+      </c>
+      <c r="AD4">
+        <v>1.07</v>
+      </c>
+      <c r="AE4">
+        <v>1.02</v>
+      </c>
+      <c r="AF4">
+        <v>2.29</v>
+      </c>
+      <c r="AG4">
+        <v>1.53</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.4</v>
+      </c>
+      <c r="AK4">
         <v>1.36</v>
-      </c>
-      <c r="AC4">
-        <v>5.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.08</v>
-      </c>
-      <c r="AE4">
-        <v>1.01</v>
-      </c>
-      <c r="AF4">
-        <v>2.22</v>
-      </c>
-      <c r="AG4">
-        <v>1.56</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.33</v>
-      </c>
-      <c r="AK4">
-        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
         <v>1.01</v>
       </c>
       <c r="X5">
+        <v>1.13</v>
+      </c>
+      <c r="Y5">
+        <v>1.7</v>
+      </c>
+      <c r="Z5">
+        <v>1.99</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+      <c r="AB5">
+        <v>1.36</v>
+      </c>
+      <c r="AC5">
+        <v>8</v>
+      </c>
+      <c r="AD5">
         <v>1.06</v>
-      </c>
-      <c r="Y5">
-        <v>1.53</v>
-      </c>
-      <c r="Z5">
-        <v>2.28</v>
-      </c>
-      <c r="AA5">
-        <v>2.75</v>
-      </c>
-      <c r="AB5">
-        <v>1.37</v>
-      </c>
-      <c r="AC5">
-        <v>5.55</v>
-      </c>
-      <c r="AD5">
-        <v>1.08</v>
       </c>
       <c r="AE5">
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="AG5">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="O6">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="P6">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1302,13 +1302,13 @@
         <v>1.83</v>
       </c>
       <c r="S6">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T6">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V6">
         <v>1.2</v>
@@ -1317,50 +1317,50 @@
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Z6">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AA6">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AB6">
         <v>1.36</v>
       </c>
       <c r="AC6">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE6">
         <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AG6">
+        <v>1.53</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.3</v>
+      </c>
+      <c r="AK6">
         <v>1.5</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.36</v>
-      </c>
-      <c r="AK6">
-        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>6.1</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.25</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q13">
         <v>2.64</v>
@@ -2443,7 +2443,7 @@
         <v>2.03</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
         <v>2.88</v>
@@ -2452,7 +2452,7 @@
         <v>2.72</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2470,7 +2470,7 @@
         <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S14">
         <v>1.1</v>
@@ -2621,7 +2621,7 @@
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.06</v>
@@ -2630,10 +2630,10 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB14">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AC14">
         <v>1.65</v>
@@ -2648,7 +2648,7 @@
         <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P15">
         <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2787,22 +2787,22 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB15">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE15">
         <v>1.17</v>
@@ -3119,10 +3119,10 @@
         <v>2.96</v>
       </c>
       <c r="AA17">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>3.14</v>
@@ -3134,10 +3134,10 @@
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
         <v>2.44</v>
@@ -3409,7 +3409,7 @@
         <v>1.33</v>
       </c>
       <c r="O19">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P19">
         <v>7.35</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
+        <v>3.2</v>
+      </c>
+      <c r="O2">
+        <v>3.3</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>3.8</v>
+      </c>
+      <c r="R2">
+        <v>2.15</v>
+      </c>
+      <c r="S2">
+        <v>1.33</v>
+      </c>
+      <c r="T2">
+        <v>2.67</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
+        <v>1.37</v>
+      </c>
+      <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
+        <v>3.43</v>
+      </c>
+      <c r="AA2">
+        <v>1.95</v>
+      </c>
+      <c r="AB2">
         <v>1.8</v>
       </c>
-      <c r="O2">
+      <c r="AC2">
         <v>3.4</v>
       </c>
-      <c r="P2">
-        <v>3.6</v>
-      </c>
-      <c r="Q2">
-        <v>2.41</v>
-      </c>
-      <c r="R2">
-        <v>2.25</v>
-      </c>
-      <c r="S2">
-        <v>1.3</v>
-      </c>
-      <c r="T2">
-        <v>3.2</v>
-      </c>
-      <c r="U2">
-        <v>2.5</v>
-      </c>
-      <c r="V2">
-        <v>1.44</v>
-      </c>
-      <c r="W2">
-        <v>1.07</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.25</v>
-      </c>
-      <c r="Z2">
-        <v>3.86</v>
-      </c>
-      <c r="AA2">
-        <v>1.76</v>
-      </c>
-      <c r="AB2">
-        <v>1.92</v>
-      </c>
-      <c r="AC2">
-        <v>2.97</v>
-      </c>
       <c r="AD2">
+        <v>1.26</v>
+      </c>
+      <c r="AE2">
+        <v>1.05</v>
+      </c>
+      <c r="AF2">
+        <v>1.75</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.33</v>
       </c>
-      <c r="AE2">
-        <v>1.14</v>
-      </c>
-      <c r="AF2">
-        <v>1.67</v>
-      </c>
-      <c r="AG2">
-        <v>2.05</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.3</v>
-      </c>
       <c r="AK2">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.8</v>
+      </c>
+      <c r="O3">
+        <v>3.4</v>
+      </c>
+      <c r="P3">
+        <v>3.6</v>
+      </c>
+      <c r="Q3">
+        <v>2.41</v>
+      </c>
+      <c r="R3">
+        <v>2.25</v>
+      </c>
+      <c r="S3">
+        <v>1.3</v>
+      </c>
+      <c r="T3">
         <v>3.2</v>
       </c>
-      <c r="O3">
-        <v>3.3</v>
-      </c>
-      <c r="P3">
-        <v>2</v>
-      </c>
-      <c r="Q3">
-        <v>3.8</v>
-      </c>
-      <c r="R3">
-        <v>2.15</v>
-      </c>
-      <c r="S3">
+      <c r="U3">
+        <v>2.5</v>
+      </c>
+      <c r="V3">
+        <v>1.44</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.86</v>
+      </c>
+      <c r="AA3">
+        <v>1.76</v>
+      </c>
+      <c r="AB3">
+        <v>1.92</v>
+      </c>
+      <c r="AC3">
+        <v>2.97</v>
+      </c>
+      <c r="AD3">
         <v>1.33</v>
       </c>
-      <c r="T3">
-        <v>2.67</v>
-      </c>
-      <c r="U3">
-        <v>2.75</v>
-      </c>
-      <c r="V3">
-        <v>1.37</v>
-      </c>
-      <c r="W3">
-        <v>1.05</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
+        <v>1.67</v>
+      </c>
+      <c r="AG3">
+        <v>2.05</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.3</v>
       </c>
-      <c r="Z3">
-        <v>3.43</v>
-      </c>
-      <c r="AA3">
-        <v>1.95</v>
-      </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
-        <v>3.4</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
-      <c r="AF3">
-        <v>1.75</v>
-      </c>
-      <c r="AG3">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.33</v>
-      </c>
       <c r="AK3">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O4">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="P4">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="S4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U4">
         <v>4.8</v>
@@ -994,31 +994,31 @@
         <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z4">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AA4">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="AB4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AC4">
         <v>5.8</v>
       </c>
       <c r="AD4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,28 +1133,28 @@
         <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S5">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y5">
         <v>1.7</v>
@@ -1163,22 +1163,22 @@
         <v>1.99</v>
       </c>
       <c r="AA5">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AB5">
         <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AD5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AG5">
         <v>1.47</v>
@@ -1296,16 +1296,16 @@
         <v>3.7</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R6">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="S6">
         <v>1.61</v>
       </c>
       <c r="T6">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
         <v>4.1</v>
@@ -1317,7 +1317,7 @@
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
         <v>1.59</v>
@@ -1329,22 +1329,22 @@
         <v>2.75</v>
       </c>
       <c r="AB6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="AD6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE6">
         <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
         <v>1.5</v>
@@ -1948,10 +1948,10 @@
         <v>6.1</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1981,10 +1981,10 @@
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD10">
         <v>1.28</v>
@@ -1993,10 +1993,10 @@
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG10">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O12">
         <v>5.25</v>
@@ -2322,7 +2322,7 @@
         <v>2.57</v>
       </c>
       <c r="AG12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="S14">
         <v>1.1</v>
@@ -2639,7 +2639,7 @@
         <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE14">
         <v>1.5</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O16">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P16">
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S16">
         <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U16">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB16">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC16">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD16">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.07</v>
       </c>
       <c r="AK16">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q17">
         <v>2.07</v>
@@ -3095,16 +3095,16 @@
         <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="U17">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3119,10 +3119,10 @@
         <v>2.96</v>
       </c>
       <c r="AA17">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC17">
         <v>3.14</v>
@@ -3134,10 +3134,10 @@
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK17">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
         <v>1.17</v>
@@ -3316,7 +3316,7 @@
         <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
+        <v>1.8</v>
+      </c>
+      <c r="O2">
+        <v>3.4</v>
+      </c>
+      <c r="P2">
+        <v>3.6</v>
+      </c>
+      <c r="Q2">
+        <v>2.41</v>
+      </c>
+      <c r="R2">
+        <v>2.25</v>
+      </c>
+      <c r="S2">
+        <v>1.3</v>
+      </c>
+      <c r="T2">
         <v>3.2</v>
       </c>
-      <c r="O2">
-        <v>3.3</v>
-      </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="Q2">
-        <v>3.8</v>
-      </c>
-      <c r="R2">
-        <v>2.15</v>
-      </c>
-      <c r="S2">
+      <c r="U2">
+        <v>2.5</v>
+      </c>
+      <c r="V2">
+        <v>1.44</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>3.86</v>
+      </c>
+      <c r="AA2">
+        <v>1.76</v>
+      </c>
+      <c r="AB2">
+        <v>1.92</v>
+      </c>
+      <c r="AC2">
+        <v>2.97</v>
+      </c>
+      <c r="AD2">
         <v>1.33</v>
       </c>
-      <c r="T2">
-        <v>2.67</v>
-      </c>
-      <c r="U2">
-        <v>2.75</v>
-      </c>
-      <c r="V2">
-        <v>1.37</v>
-      </c>
-      <c r="W2">
-        <v>1.05</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
-      <c r="Y2">
+      <c r="AE2">
+        <v>1.14</v>
+      </c>
+      <c r="AF2">
+        <v>1.67</v>
+      </c>
+      <c r="AG2">
+        <v>2.05</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.3</v>
       </c>
-      <c r="Z2">
-        <v>3.43</v>
-      </c>
-      <c r="AA2">
-        <v>1.95</v>
-      </c>
-      <c r="AB2">
-        <v>1.8</v>
-      </c>
-      <c r="AC2">
-        <v>3.4</v>
-      </c>
-      <c r="AD2">
-        <v>1.26</v>
-      </c>
-      <c r="AE2">
-        <v>1.05</v>
-      </c>
-      <c r="AF2">
-        <v>1.75</v>
-      </c>
-      <c r="AG2">
-        <v>2</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.33</v>
-      </c>
       <c r="AK2">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
+        <v>3.2</v>
+      </c>
+      <c r="O3">
+        <v>3.3</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>3.8</v>
+      </c>
+      <c r="R3">
+        <v>2.15</v>
+      </c>
+      <c r="S3">
+        <v>1.33</v>
+      </c>
+      <c r="T3">
+        <v>2.67</v>
+      </c>
+      <c r="U3">
+        <v>2.75</v>
+      </c>
+      <c r="V3">
+        <v>1.37</v>
+      </c>
+      <c r="W3">
+        <v>1.05</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
+        <v>3.43</v>
+      </c>
+      <c r="AA3">
+        <v>1.95</v>
+      </c>
+      <c r="AB3">
         <v>1.8</v>
       </c>
-      <c r="O3">
+      <c r="AC3">
         <v>3.4</v>
       </c>
-      <c r="P3">
-        <v>3.6</v>
-      </c>
-      <c r="Q3">
-        <v>2.41</v>
-      </c>
-      <c r="R3">
-        <v>2.25</v>
-      </c>
-      <c r="S3">
-        <v>1.3</v>
-      </c>
-      <c r="T3">
-        <v>3.2</v>
-      </c>
-      <c r="U3">
-        <v>2.5</v>
-      </c>
-      <c r="V3">
-        <v>1.44</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
-      <c r="Y3">
-        <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.86</v>
-      </c>
-      <c r="AA3">
-        <v>1.76</v>
-      </c>
-      <c r="AB3">
-        <v>1.92</v>
-      </c>
-      <c r="AC3">
-        <v>2.97</v>
-      </c>
       <c r="AD3">
+        <v>1.26</v>
+      </c>
+      <c r="AE3">
+        <v>1.05</v>
+      </c>
+      <c r="AF3">
+        <v>1.75</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.33</v>
       </c>
-      <c r="AE3">
-        <v>1.14</v>
-      </c>
-      <c r="AF3">
-        <v>1.67</v>
-      </c>
-      <c r="AG3">
-        <v>2.05</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.3</v>
-      </c>
       <c r="AK3">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z4">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AA4">
         <v>3.21</v>
       </c>
       <c r="AB4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AC4">
         <v>5.8</v>
       </c>
       <c r="AD4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AG4">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         <v>1.72</v>
       </c>
       <c r="T5">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
         <v>4</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
         <v>1.02</v>
@@ -1163,7 +1163,7 @@
         <v>1.99</v>
       </c>
       <c r="AA5">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AB5">
         <v>1.36</v>
@@ -1178,7 +1178,7 @@
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AG5">
         <v>1.47</v>
@@ -1329,7 +1329,7 @@
         <v>2.75</v>
       </c>
       <c r="AB6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC6">
         <v>6.15</v>
@@ -1341,10 +1341,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>3.25</v>
       </c>
       <c r="P13">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
         <v>2.64</v>
@@ -2461,10 +2461,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
         <v>1.7</v>
@@ -2621,7 +2621,7 @@
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.06</v>
@@ -2639,7 +2639,7 @@
         <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AE14">
         <v>1.5</v>
@@ -2763,10 +2763,10 @@
         <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -3089,22 +3089,22 @@
         <v>6.25</v>
       </c>
       <c r="Q17">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="R17">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="U17">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3119,25 +3119,25 @@
         <v>2.96</v>
       </c>
       <c r="AA17">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1.33</v>
       </c>
       <c r="O19">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P19">
         <v>7.35</v>
@@ -3430,7 +3430,7 @@
         <v>2.04</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W19">
         <v>1.16</v>
@@ -3451,10 +3451,10 @@
         <v>2.46</v>
       </c>
       <c r="AC19">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD19">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE19">
         <v>1.25</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="Q2">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R2">
         <v>2.25</v>
@@ -656,7 +656,7 @@
         <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
         <v>1.44</v>
@@ -671,7 +671,7 @@
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="AA2">
         <v>1.76</v>
@@ -680,10 +680,10 @@
         <v>1.92</v>
       </c>
       <c r="AC2">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE2">
         <v>1.14</v>
@@ -801,19 +801,19 @@
         <v>3.2</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
         <v>2.67</v>
@@ -825,25 +825,25 @@
         <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="AA3">
         <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
         <v>1.26</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>4.38</v>
       </c>
       <c r="O7">
         <v>3.5</v>
@@ -1459,7 +1459,7 @@
         <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="R7">
         <v>2.05</v>
@@ -1480,7 +1480,7 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.24</v>
@@ -1492,22 +1492,22 @@
         <v>1.84</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O8">
-        <v>5.35</v>
+        <v>6.75</v>
       </c>
       <c r="P8">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>1.57</v>
@@ -1652,25 +1652,25 @@
         <v>5.55</v>
       </c>
       <c r="AA8">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB8">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC8">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AD8">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AE8">
         <v>1.28</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         <v>1.22</v>
       </c>
       <c r="O12">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q12">
         <v>1.67</v>
@@ -2461,16 +2461,16 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2769,13 +2769,13 @@
         <v>2.48</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
         <v>1.59</v>
@@ -2938,7 +2938,7 @@
         <v>3.9</v>
       </c>
       <c r="U16">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V16">
         <v>1.63</v>
@@ -2962,10 +2962,10 @@
         <v>2.5</v>
       </c>
       <c r="AC16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE16">
         <v>1.25</v>
@@ -3246,10 +3246,10 @@
         <v>1.91</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -3430,7 +3430,7 @@
         <v>2.04</v>
       </c>
       <c r="V19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
         <v>1.16</v>
@@ -3448,13 +3448,13 @@
         <v>1.43</v>
       </c>
       <c r="AB19">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC19">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD19">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE19">
         <v>1.25</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -1957,13 +1957,13 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
         <v>1.06</v>
@@ -1981,10 +1981,10 @@
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD10">
         <v>1.28</v>
@@ -1993,10 +1993,10 @@
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
         <v>2.63</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>3.73</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>4.68</v>
+        <v>7.25</v>
       </c>
       <c r="Q11">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
         <v>1.27</v>
@@ -2175,7 +2175,7 @@
         <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.25</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>2.64</v>
@@ -2452,7 +2452,7 @@
         <v>2.72</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="O14">
         <v>5.5</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="S14">
         <v>1.1</v>
@@ -2612,10 +2612,10 @@
         <v>5.1</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V14">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="W14">
         <v>1.29</v>
@@ -2763,10 +2763,10 @@
         <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="R15">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2778,7 +2778,7 @@
         <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W15">
         <v>1.13</v>
@@ -2787,10 +2787,10 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA15">
         <v>1.54</v>
@@ -2799,10 +2799,10 @@
         <v>2.27</v>
       </c>
       <c r="AC15">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD15">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE15">
         <v>1.17</v>
@@ -2923,7 +2923,7 @@
         <v>5.25</v>
       </c>
       <c r="P16">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q16">
         <v>1.62</v>
@@ -2935,7 +2935,7 @@
         <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
         <v>2.1</v>
@@ -2944,7 +2944,7 @@
         <v>1.63</v>
       </c>
       <c r="W16">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X16">
         <v>1.02</v>
@@ -2956,10 +2956,10 @@
         <v>5.75</v>
       </c>
       <c r="AA16">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB16">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC16">
         <v>2.06</v>
@@ -3086,7 +3086,7 @@
         <v>3.9</v>
       </c>
       <c r="P17">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>1.96</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
         <v>5.3</v>
@@ -3424,46 +3424,46 @@
         <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="U19">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z19">
-        <v>5.15</v>
+        <v>5.35</v>
       </c>
       <c r="AA19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
         <v>2.6</v>
       </c>
       <c r="AC19">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD19">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF19">
         <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
+        <v>3.2</v>
+      </c>
+      <c r="O2">
+        <v>3.2</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>3.5</v>
+      </c>
+      <c r="R2">
+        <v>2.03</v>
+      </c>
+      <c r="S2">
+        <v>1.41</v>
+      </c>
+      <c r="T2">
+        <v>2.62</v>
+      </c>
+      <c r="U2">
+        <v>2.8</v>
+      </c>
+      <c r="V2">
+        <v>1.37</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
+        <v>3.48</v>
+      </c>
+      <c r="AA2">
+        <v>1.95</v>
+      </c>
+      <c r="AB2">
         <v>1.78</v>
       </c>
-      <c r="O2">
-        <v>3.23</v>
-      </c>
-      <c r="P2">
-        <v>3.23</v>
-      </c>
-      <c r="Q2">
-        <v>2.42</v>
-      </c>
-      <c r="R2">
-        <v>2.25</v>
-      </c>
-      <c r="S2">
-        <v>1.3</v>
-      </c>
-      <c r="T2">
+      <c r="AC2">
         <v>3.2</v>
       </c>
-      <c r="U2">
-        <v>2.6</v>
-      </c>
-      <c r="V2">
-        <v>1.44</v>
-      </c>
-      <c r="W2">
-        <v>1.07</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.25</v>
-      </c>
-      <c r="Z2">
-        <v>3.89</v>
-      </c>
-      <c r="AA2">
-        <v>1.76</v>
-      </c>
-      <c r="AB2">
-        <v>1.92</v>
-      </c>
-      <c r="AC2">
-        <v>2.88</v>
-      </c>
       <c r="AD2">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G3">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.51</v>
+      </c>
+      <c r="O3">
+        <v>3.71</v>
+      </c>
+      <c r="P3">
+        <v>4.05</v>
+      </c>
+      <c r="Q3">
+        <v>2.3</v>
+      </c>
+      <c r="R3">
+        <v>2.25</v>
+      </c>
+      <c r="S3">
+        <v>1.3</v>
+      </c>
+      <c r="T3">
         <v>3.2</v>
       </c>
-      <c r="O3">
-        <v>3.25</v>
-      </c>
-      <c r="P3">
-        <v>1.98</v>
-      </c>
-      <c r="Q3">
-        <v>3.8</v>
-      </c>
-      <c r="R3">
-        <v>2.03</v>
-      </c>
-      <c r="S3">
-        <v>1.4</v>
-      </c>
-      <c r="T3">
-        <v>2.67</v>
-      </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.46</v>
+        <v>4.05</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG3">
         <v>2</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P4">
         <v>2.75</v>
@@ -1015,10 +1015,10 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1136,13 +1136,13 @@
         <v>3.65</v>
       </c>
       <c r="R5">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="S5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T5">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -1326,7 +1326,7 @@
         <v>2.17</v>
       </c>
       <c r="AA6">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AB6">
         <v>1.36</v>
@@ -1459,10 +1459,10 @@
         <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>5.14</v>
+        <v>5.31</v>
       </c>
       <c r="R7">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S7">
         <v>1.33</v>
@@ -1474,7 +1474,7 @@
         <v>2.59</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.08</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
         <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="S14">
         <v>1.1</v>
@@ -2621,7 +2621,7 @@
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.06</v>
@@ -2639,7 +2639,7 @@
         <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AE14">
         <v>1.5</v>
@@ -3264,7 +3264,7 @@
         <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="V18">
         <v>1.71</v>
@@ -3288,10 +3288,10 @@
         <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AD18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE18">
         <v>1.29</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -603,25 +603,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,111 +631,111 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
+        <v>1.51</v>
+      </c>
+      <c r="O2">
+        <v>3.71</v>
+      </c>
+      <c r="P2">
+        <v>4.05</v>
+      </c>
+      <c r="Q2">
+        <v>2.3</v>
+      </c>
+      <c r="R2">
+        <v>2.25</v>
+      </c>
+      <c r="S2">
+        <v>1.3</v>
+      </c>
+      <c r="T2">
         <v>3.2</v>
       </c>
-      <c r="O2">
-        <v>3.2</v>
-      </c>
-      <c r="P2">
+      <c r="U2">
+        <v>2.5</v>
+      </c>
+      <c r="V2">
+        <v>1.44</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.24</v>
+      </c>
+      <c r="Z2">
+        <v>4.05</v>
+      </c>
+      <c r="AA2">
+        <v>1.76</v>
+      </c>
+      <c r="AB2">
+        <v>1.92</v>
+      </c>
+      <c r="AC2">
+        <v>2.83</v>
+      </c>
+      <c r="AD2">
+        <v>1.33</v>
+      </c>
+      <c r="AE2">
+        <v>1.15</v>
+      </c>
+      <c r="AF2">
+        <v>1.7</v>
+      </c>
+      <c r="AG2">
         <v>2</v>
       </c>
-      <c r="Q2">
-        <v>3.5</v>
-      </c>
-      <c r="R2">
-        <v>2.03</v>
-      </c>
-      <c r="S2">
-        <v>1.41</v>
-      </c>
-      <c r="T2">
-        <v>2.62</v>
-      </c>
-      <c r="U2">
-        <v>2.8</v>
-      </c>
-      <c r="V2">
-        <v>1.37</v>
-      </c>
-      <c r="W2">
-        <v>1.06</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
-      <c r="Y2">
-        <v>1.3</v>
-      </c>
-      <c r="Z2">
-        <v>3.48</v>
-      </c>
-      <c r="AA2">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>["8", "42"]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>["31"]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.29</v>
+      </c>
+      <c r="AK2">
         <v>1.95</v>
       </c>
-      <c r="AB2">
-        <v>1.78</v>
-      </c>
-      <c r="AC2">
-        <v>3.2</v>
-      </c>
-      <c r="AD2">
-        <v>1.26</v>
-      </c>
-      <c r="AE2">
-        <v>1.05</v>
-      </c>
-      <c r="AF2">
-        <v>1.75</v>
-      </c>
-      <c r="AG2">
-        <v>1.93</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.33</v>
-      </c>
-      <c r="AK2">
-        <v>1.29</v>
-      </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,118 +787,118 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>4.05</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
+        <v>1.41</v>
+      </c>
+      <c r="T3">
+        <v>2.62</v>
+      </c>
+      <c r="U3">
+        <v>2.8</v>
+      </c>
+      <c r="V3">
+        <v>1.37</v>
+      </c>
+      <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
         <v>1.3</v>
       </c>
-      <c r="T3">
+      <c r="Z3">
+        <v>3.48</v>
+      </c>
+      <c r="AA3">
+        <v>1.95</v>
+      </c>
+      <c r="AB3">
+        <v>1.78</v>
+      </c>
+      <c r="AC3">
         <v>3.2</v>
       </c>
-      <c r="U3">
-        <v>2.5</v>
-      </c>
-      <c r="V3">
-        <v>1.44</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
-      <c r="Y3">
-        <v>1.24</v>
-      </c>
-      <c r="Z3">
-        <v>4.05</v>
-      </c>
-      <c r="AA3">
-        <v>1.76</v>
-      </c>
-      <c r="AB3">
-        <v>1.92</v>
-      </c>
-      <c r="AC3">
-        <v>2.83</v>
-      </c>
       <c r="AD3">
+        <v>1.26</v>
+      </c>
+      <c r="AE3">
+        <v>1.05</v>
+      </c>
+      <c r="AF3">
+        <v>1.75</v>
+      </c>
+      <c r="AG3">
+        <v>1.93</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.33</v>
       </c>
-      <c r="AE3">
-        <v>1.15</v>
-      </c>
-      <c r="AF3">
-        <v>1.7</v>
-      </c>
-      <c r="AG3">
+      <c r="AK3">
+        <v>1.29</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
         <v>2</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.29</v>
-      </c>
-      <c r="AK3">
-        <v>1.95</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-1</v>
-      </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="O5">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="P5">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="R5">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="S5">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="T5">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Z5">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AA5">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="AB5">
         <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>7.1</v>
+        <v>6.15</v>
       </c>
       <c r="AD5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AG5">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.02</v>
+        <v>4.38</v>
       </c>
       <c r="O6">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q6">
-        <v>3.12</v>
+        <v>5.31</v>
       </c>
       <c r="R6">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="S6">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
         <v>1.01</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
+        <v>1.22</v>
+      </c>
+      <c r="Z6">
+        <v>3.6</v>
+      </c>
+      <c r="AA6">
+        <v>1.81</v>
+      </c>
+      <c r="AB6">
+        <v>1.91</v>
+      </c>
+      <c r="AC6">
+        <v>2.97</v>
+      </c>
+      <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
         <v>1.07</v>
       </c>
-      <c r="Y6">
-        <v>1.59</v>
-      </c>
-      <c r="Z6">
-        <v>2.17</v>
-      </c>
-      <c r="AA6">
-        <v>2.83</v>
-      </c>
-      <c r="AB6">
-        <v>1.36</v>
-      </c>
-      <c r="AC6">
-        <v>6.15</v>
-      </c>
-      <c r="AD6">
-        <v>1.06</v>
-      </c>
-      <c r="AE6">
-        <v>1.02</v>
-      </c>
       <c r="AF6">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.38</v>
+        <v>1.22</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="P7">
-        <v>1.65</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>5.31</v>
+        <v>1.57</v>
       </c>
       <c r="R7">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>5.55</v>
       </c>
       <c r="AA7">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AC7">
-        <v>2.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>1.11</v>
+        <v>4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:00:00</t>
+          <t>2026-10-22 09:15:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15:00</t>
+          <t>2026-10-22 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>6.1</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="U10">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O12">
         <v>5</v>
       </c>
       <c r="P12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="U12">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2298,22 +2298,22 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2443,28 +2443,28 @@
         <v>2.03</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
         <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.14</v>
+        <v>3.67</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
@@ -2473,19 +2473,19 @@
         <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2597,58 +2597,58 @@
         <v>5.5</v>
       </c>
       <c r="P14">
+        <v>1.25</v>
+      </c>
+      <c r="Q14">
+        <v>6.5</v>
+      </c>
+      <c r="R14">
+        <v>3.01</v>
+      </c>
+      <c r="S14">
+        <v>1.08</v>
+      </c>
+      <c r="T14">
+        <v>5.7</v>
+      </c>
+      <c r="U14">
+        <v>1.68</v>
+      </c>
+      <c r="V14">
+        <v>2.08</v>
+      </c>
+      <c r="W14">
         <v>1.3</v>
-      </c>
-      <c r="Q14">
-        <v>6</v>
-      </c>
-      <c r="R14">
-        <v>3.25</v>
-      </c>
-      <c r="S14">
-        <v>1.1</v>
-      </c>
-      <c r="T14">
-        <v>5.1</v>
-      </c>
-      <c r="U14">
-        <v>1.75</v>
-      </c>
-      <c r="V14">
-        <v>1.93</v>
-      </c>
-      <c r="W14">
-        <v>1.29</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB14">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AC14">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AD14">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AE14">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG14">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AK14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>1.54</v>
       </c>
       <c r="AB15">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AC15">
         <v>2.29</v>
@@ -3080,37 +3080,37 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q17">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U17">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.33</v>
@@ -3119,25 +3119,25 @@
         <v>2.96</v>
       </c>
       <c r="AA17">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC17">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,25 +3252,25 @@
         <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,25 +3282,25 @@
         <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
         <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD18">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG18">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
         <v>5.3</v>
@@ -3424,46 +3424,46 @@
         <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U19">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC19">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AD19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE19">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF19">
         <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1276,14 +1276,14 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1442,81 +1442,81 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
+        <v>1.08</v>
+      </c>
+      <c r="O7">
+        <v>6.25</v>
+      </c>
+      <c r="P7">
+        <v>12</v>
+      </c>
+      <c r="Q7">
+        <v>1.44</v>
+      </c>
+      <c r="R7">
+        <v>2.8</v>
+      </c>
+      <c r="S7">
         <v>1.22</v>
       </c>
-      <c r="O7">
-        <v>6.75</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
+      <c r="T7">
+        <v>3.75</v>
+      </c>
+      <c r="U7">
+        <v>2.1</v>
+      </c>
+      <c r="V7">
+        <v>1.67</v>
+      </c>
+      <c r="W7">
+        <v>1.17</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>5.05</v>
+      </c>
+      <c r="AA7">
+        <v>1.45</v>
+      </c>
+      <c r="AB7">
+        <v>2.5</v>
+      </c>
+      <c r="AC7">
+        <v>2.1</v>
+      </c>
+      <c r="AD7">
         <v>1.57</v>
       </c>
-      <c r="R7">
-        <v>2.9</v>
-      </c>
-      <c r="S7">
-        <v>1.2</v>
-      </c>
-      <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
+      <c r="AE7">
+        <v>1.23</v>
+      </c>
+      <c r="AF7">
         <v>1.95</v>
       </c>
-      <c r="V7">
-        <v>1.75</v>
-      </c>
-      <c r="W7">
-        <v>1.2</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.08</v>
-      </c>
-      <c r="Z7">
-        <v>5.55</v>
-      </c>
-      <c r="AA7">
-        <v>1.36</v>
-      </c>
-      <c r="AB7">
-        <v>2.7</v>
-      </c>
-      <c r="AC7">
-        <v>1.96</v>
-      </c>
-      <c r="AD7">
-        <v>1.72</v>
-      </c>
-      <c r="AE7">
-        <v>1.28</v>
-      </c>
-      <c r="AF7">
-        <v>1.87</v>
-      </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "54", "90+4"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "49", "57", "66"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "84", "90+4"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2434,7 +2434,7 @@
         <v>3.25</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
         <v>2.64</v>
@@ -2443,16 +2443,16 @@
         <v>2.03</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U13">
         <v>2.61</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2461,10 +2461,10 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z13">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
@@ -2473,16 +2473,16 @@
         <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
         <v>2.01</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
         <v>2.05</v>
       </c>
       <c r="Q15">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="R15">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2775,40 +2775,40 @@
         <v>3.5</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA15">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB15">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AC15">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AD15">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
         <v>2.45</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
+        <v>1.22</v>
+      </c>
+      <c r="AK15">
         <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>3.8</v>
       </c>
       <c r="U16">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V16">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W16">
         <v>1.16</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.1</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
         <v>3.8</v>
@@ -3409,7 +3409,7 @@
         <v>1.33</v>
       </c>
       <c r="O19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P19">
         <v>7.35</v>
@@ -3421,49 +3421,49 @@
         <v>2.62</v>
       </c>
       <c r="S19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="U19">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
         <v>1.16</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA19">
         <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD19">
         <v>1.62</v>
       </c>
       <c r="AE19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
         <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
         <v>3.6</v>

--- a/jogos_2026-10-22.xlsx
+++ b/jogos_2026-10-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2098,111 +2098,111 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P11">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R11">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
+        <v>1.19</v>
+      </c>
+      <c r="Z11">
+        <v>4.06</v>
+      </c>
+      <c r="AA11">
+        <v>1.63</v>
+      </c>
+      <c r="AB11">
+        <v>2.15</v>
+      </c>
+      <c r="AC11">
+        <v>2.75</v>
+      </c>
+      <c r="AD11">
+        <v>1.4</v>
+      </c>
+      <c r="AE11">
+        <v>1.14</v>
+      </c>
+      <c r="AF11">
+        <v>1.77</v>
+      </c>
+      <c r="AG11">
+        <v>1.91</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>["18", "32"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>["11"]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.18</v>
       </c>
-      <c r="Z11">
-        <v>4.2</v>
-      </c>
-      <c r="AA11">
-        <v>1.64</v>
-      </c>
-      <c r="AB11">
-        <v>2.17</v>
-      </c>
-      <c r="AC11">
-        <v>2.53</v>
-      </c>
-      <c r="AD11">
-        <v>1.44</v>
-      </c>
-      <c r="AE11">
-        <v>1.15</v>
-      </c>
-      <c r="AF11">
-        <v>1.81</v>
-      </c>
-      <c r="AG11">
-        <v>1.86</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.15</v>
-      </c>
       <c r="AK11">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "89"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "69"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,23 +2571,23 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "28", "51", "70"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "31", "54"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2906,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "60", "63"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "78", "90+1"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3235,24 +3235,24 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
         <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
         <v>2.47</v>
@@ -3267,7 +3267,7 @@
         <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
         <v>1.18</v>
@@ -3276,10 +3276,10 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>1.36</v>
@@ -3288,13 +3288,13 @@
         <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
         <v>1.38</v>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "36"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "90+3"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>7.35</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00:00</t>
+          <t>2026-10-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G20">
@@ -3672,169 +3672,6 @@
         <v>0</v>
       </c>
       <c r="AU20" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sidama Bunna</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Awassa Kenema</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
         <is>
           <t>2026-10-22 21:00:00</t>
         </is>
